--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484659_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484659_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9308</v>
+        <v>6.1703</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0678</v>
+        <v>5.2329</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8631</v>
+        <v>0.9374</v>
       </c>
       <c r="G2" t="n">
         <v>1.7841</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4263</v>
+        <v>-0.1869</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4419</v>
+        <v>-0.2767</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0156</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>4.7563</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5389</v>
+        <v>4.3572</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8158</v>
+        <v>5.981</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.277</v>
+        <v>-1.6238</v>
       </c>
       <c r="G3" t="n">
         <v>3.7425</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1928</v>
+        <v>-0.3744</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.497</v>
+        <v>-0.3318</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3042</v>
+        <v>-0.0426</v>
       </c>
       <c r="V3" t="n">
         <v>3.1882</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.994</v>
+        <v>2.3955</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2337</v>
+        <v>2.5361</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2397</v>
+        <v>-0.1406</v>
       </c>
       <c r="G4" t="n">
         <v>0.716</v>
@@ -766,13 +766,13 @@
         <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1722</v>
+        <v>0.2293</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2391</v>
+        <v>0.0634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0668</v>
+        <v>0.1659</v>
       </c>
       <c r="V4" t="n">
         <v>1.267</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1961</v>
+        <v>0.9502</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4084</v>
+        <v>0.9502</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2123</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1243</v>
+        <v>0.9502</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.781</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6566</v>
+        <v>0.6251</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5736</v>
+        <v>0.9502</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3652</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2084</v>
+        <v>0.6251</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6979</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1462</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4483</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8152</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0785</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7368</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9502</v>
+        <v>-0.0136</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9502</v>
+        <v>2.6942</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-2.7077</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9502</v>
+        <v>-1.1243</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-1.781</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6251</v>
+        <v>0.6566</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9502</v>
+        <v>0.5736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>0.3652</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6251</v>
+        <v>0.2084</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.6979</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.1462</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.4483</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.6056</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3643</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2413</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.6713</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2227</v>
+        <v>-0.1266</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="G7" t="n">
         <v>-0.117</v>
@@ -1000,13 +1000,13 @@
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>0.033</v>
+        <v>0.1787</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. BOYENZA</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3387</v>
+        <v>-1.4554</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4191</v>
+        <v>-2.3085</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9196</v>
+        <v>0.8531</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7003</v>
+        <v>-1.1354</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.306</v>
+        <v>-3.3374</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6057</v>
+        <v>2.2021</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1684</v>
+        <v>-1.2097</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0433</v>
+        <v>-1.9697</v>
       </c>
       <c r="L8" t="n">
-        <v>0.125</v>
+        <v>0.76</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8686</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3493</v>
+        <v>-1.3677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4807</v>
+        <v>1.4421</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>0.317</v>
+        <v>-0.4483</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3288</v>
+        <v>-0.3499</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0119</v>
+        <v>-0.0984</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9554</v>
+        <v>0.3115</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
         <v>-0.9554</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LOZANO CATALA</t>
+          <t>S. BOYENZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9783</v>
+        <v>-1.5914</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4172</v>
+        <v>-0.5975</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.9939</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5512</v>
+        <v>-0.7003</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9775</v>
+        <v>-1.306</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4263</v>
+        <v>0.6057</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.197</v>
+        <v>0.1684</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2387</v>
+        <v>0.0433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0417</v>
+        <v>0.125</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3541</v>
+        <v>-0.8686</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7388</v>
+        <v>-1.3493</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3846</v>
+        <v>0.4807</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4271</v>
+        <v>0.0643</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2202</v>
+        <v>0.1505</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2069</v>
+        <v>-0.0862</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>S. LOZANO CATALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1979</v>
+        <v>-1.6566</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8032</v>
+        <v>-1.1699</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.4867</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1354</v>
+        <v>-1.5512</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.3374</v>
+        <v>-1.9775</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2021</v>
+        <v>0.4263</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2097</v>
+        <v>-1.197</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9697</v>
+        <v>-1.2387</v>
       </c>
       <c r="L10" t="n">
-        <v>0.76</v>
+        <v>0.0417</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07439999999999999</v>
+        <v>-0.3541</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3677</v>
+        <v>-0.7388</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4421</v>
+        <v>0.3846</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1908</v>
+        <v>-0.1054</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8446</v>
+        <v>0.0272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3462</v>
+        <v>-0.1325</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9307</v>
+        <v>-2.3117</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7292</v>
+        <v>0.9766</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.6599</v>
+        <v>-3.2883</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9319</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9438</v>
+        <v>-0.3249</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2767</v>
+        <v>-0.0294</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6671</v>
+        <v>-0.2955</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3219</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3474</v>
+        <v>6.1732</v>
       </c>
       <c r="E12" t="n">
-        <v>13.3429</v>
+        <v>14.1685</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.9954</v>
+        <v>-7.995200000000001</v>
       </c>
       <c r="G12" t="n">
         <v>1.6327</v>
@@ -1378,7 +1378,7 @@
         <v>-14.2264</v>
       </c>
       <c r="O12" t="n">
-        <v>4.805499999999999</v>
+        <v>4.8055</v>
       </c>
       <c r="P12" t="n">
         <v>-3.6651</v>
@@ -1390,16 +1390,16 @@
         <v>10.0792</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1878</v>
+        <v>-0.362</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1122</v>
+        <v>-0.2862</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0757000000000001</v>
+        <v>-0.07550000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>8.567600000000001</v>
+        <v>8.567600000000002</v>
       </c>
       <c r="W12" t="n">
         <v>17.1458</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1693</v>
+        <v>3.7672</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7532</v>
+        <v>5.2725</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5839</v>
+        <v>-1.5052</v>
       </c>
       <c r="G13" t="n">
         <v>2.2815</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9557</v>
+        <v>0.5536</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6199</v>
+        <v>0.1392</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3357</v>
+        <v>0.4144</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0964</v>
+        <v>3.0572</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0354</v>
+        <v>4.2109</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-1.1536</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2028</v>
+        <v>2.1601</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2366</v>
+        <v>0.7909</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.4394</v>
+        <v>1.3692</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2286</v>
+        <v>3.5265</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5695</v>
+        <v>2.1891</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7981</v>
+        <v>1.3374</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9742</v>
+        <v>-1.3664</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3329</v>
+        <v>-1.3982</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6413</v>
+        <v>0.0318</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>1.496</v>
+        <v>0.0494</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4631</v>
+        <v>-0.2997</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0329</v>
+        <v>0.3492</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1539</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8009</v>
+        <v>1.9005</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6471</v>
+        <v>-1.969</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9587</v>
+        <v>2.1771</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5378</v>
+        <v>2.7854</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5791</v>
+        <v>-0.6083</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1601</v>
+        <v>-2.2028</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7909</v>
+        <v>0.2366</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3692</v>
+        <v>-2.4394</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5265</v>
+        <v>-1.2286</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1891</v>
+        <v>0.5695</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3374</v>
+        <v>-1.7981</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3664</v>
+        <v>-0.9742</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3982</v>
+        <v>-0.3329</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0318</v>
+        <v>-0.6413</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0492</v>
+        <v>0.5767</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9728</v>
+        <v>0.2131</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.3637</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.06859999999999999</v>
+        <v>2.1539</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9005</v>
+        <v>3.8009</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.969</v>
+        <v>-1.6471</v>
       </c>
     </row>
     <row r="16">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4116</v>
+        <v>-1.2736</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5523</v>
+        <v>0.6222</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-1.8957</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4363</v>
+        <v>-0.4528</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0999</v>
+        <v>1.4734</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6636</v>
+        <v>-1.9263</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7569</v>
+        <v>0.6968</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7153</v>
+        <v>1.8857</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0417</v>
+        <v>-1.1889</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3207</v>
+        <v>-1.1496</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3846</v>
+        <v>-0.4122</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7053</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0684</v>
+        <v>-0.3759</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1101</v>
+        <v>-0.0746</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1785</v>
+        <v>-0.3013</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6335</v>
+        <v>-1.9109</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4955</v>
+        <v>-1.3607</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4014</v>
+        <v>-0.4561</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8969</v>
+        <v>-0.9046</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4161</v>
+        <v>0.4363</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8585</v>
+        <v>1.0999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5577</v>
+        <v>-0.6636</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9579</v>
+        <v>0.7569</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2078</v>
+        <v>0.7153</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7501</v>
+        <v>0.0417</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5418</v>
+        <v>-0.3207</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3493</v>
+        <v>0.3846</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1925</v>
+        <v>-0.7053</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.5656</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6229</v>
+        <v>0.1193</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1086</v>
+        <v>-0.0139</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5143</v>
+        <v>0.1333</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.969</v>
+        <v>-0.6335</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.969</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6495</v>
+        <v>-1.6471</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6222</v>
+        <v>0.4976</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2717</v>
+        <v>-2.1447</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4528</v>
+        <v>2.4161</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4734</v>
+        <v>1.8585</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9263</v>
+        <v>0.5577</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6968</v>
+        <v>3.9579</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8857</v>
+        <v>3.2078</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1889</v>
+        <v>0.7501</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1496</v>
+        <v>-1.5418</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4122</v>
+        <v>-1.3493</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.1925</v>
       </c>
       <c r="P21" t="n">
-        <v>1.4661</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7519</v>
+        <v>0.4713</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0746</v>
+        <v>0.2048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6772</v>
+        <v>0.2666</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.9109</v>
+        <v>-1.969</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9109</v>
+        <v>-1.969</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9645</v>
+        <v>-2.5842</v>
       </c>
       <c r="E22" t="n">
         <v>-1.8194</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1451</v>
+        <v>-0.7648</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3843</v>
@@ -2170,13 +2170,13 @@
         <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3578</v>
+        <v>0.0224</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1297</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2281</v>
+        <v>0.1521</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4113</v>
+        <v>-3.9102</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6946</v>
+        <v>-3.9254</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2833</v>
+        <v>0.0151</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5356</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>0.232</v>
+        <v>0.733</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8077</v>
+        <v>-0.0384</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0396</v>
+        <v>0.7715</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6575</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1905</v>
+        <v>-5.8422</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8395</v>
+        <v>-2.7433</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.351</v>
+        <v>-3.0989</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9025</v>
@@ -2326,13 +2326,13 @@
         <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0283</v>
+        <v>0.32</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0211</v>
+        <v>0.0751</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0072</v>
+        <v>0.2449</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8932</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.347300000000001</v>
+        <v>-4.065300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>7.995400000000001</v>
+        <v>7.9956</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.3428</v>
+        <v>-12.0607</v>
       </c>
       <c r="G25" t="n">
         <v>-1.632799999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>7.341699999999999</v>
+        <v>7.341700000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-8.974399999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>9.420799999999998</v>
+        <v>9.4208</v>
       </c>
       <c r="K25" t="n">
         <v>14.2265</v>
@@ -2389,13 +2389,13 @@
         <v>-11.0537</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.8846</v>
+        <v>-6.884599999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.168900000000001</v>
+        <v>-4.1689</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6652</v>
+        <v>3.665200000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.0792</v>
@@ -2404,13 +2404,13 @@
         <v>13.7443</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1878</v>
+        <v>2.4698</v>
       </c>
       <c r="T25" t="n">
-        <v>0.07560000000000022</v>
+        <v>0.0759</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1122</v>
+        <v>2.3944</v>
       </c>
       <c r="V25" t="n">
         <v>-8.5677</v>
